--- a/nfl/dfs/salaries/DK_WEEK3_DELIVERABLE_SUPPLEMENT.xlsx
+++ b/nfl/dfs/salaries/DK_WEEK3_DELIVERABLE_SUPPLEMENT.xlsx
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="E2">
         <v>336</v>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>2.59</v>
+        <v>2.79</v>
       </c>
       <c r="E3">
         <v>336</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>2.57</v>
+        <v>2.77</v>
       </c>
       <c r="E4">
         <v>336</v>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>2.52</v>
+        <v>2.73</v>
       </c>
       <c r="E5">
         <v>720</v>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.77</v>
+        <v>0.98</v>
       </c>
       <c r="E6">
         <v>336</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="E7">
         <v>336</v>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.74</v>
+        <v>0.95</v>
       </c>
       <c r="E8">
         <v>336</v>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="E9">
         <v>336</v>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="E10">
         <v>720</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.71</v>
+        <v>0.92</v>
       </c>
       <c r="E11">
         <v>168</v>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="D12">
-        <v>1.98</v>
+        <v>2.19</v>
       </c>
       <c r="E12">
         <v>36</v>
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="D13">
-        <v>11.64</v>
+        <v>11.85</v>
       </c>
       <c r="E13">
         <v>6</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="D14">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="E14">
         <v>36</v>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="E15">
         <v>24</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>1790568374</v>
+        <v>1790569118</v>
       </c>
     </row>
     <row r="7">

--- a/nfl/dfs/salaries/DK_WEEK3_DELIVERABLE_SUPPLEMENT.xlsx
+++ b/nfl/dfs/salaries/DK_WEEK3_DELIVERABLE_SUPPLEMENT.xlsx
@@ -69,36 +69,36 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.5135</v>
+        <v>0.4823</v>
       </c>
       <c r="C2">
-        <v>0.5186</v>
+        <v>0.4914</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenneth Walker III</t>
+          <t xml:space="preserve">Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="B3">
-        <v>0.4158</v>
+        <v>0.3844</v>
       </c>
       <c r="C3">
-        <v>0.4144</v>
+        <v>0.3828</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaxon Smith-Njigba</t>
+          <t xml:space="preserve">Jahmyr Gibbs</t>
         </is>
       </c>
       <c r="B4">
-        <v>0.3686</v>
+        <v>0.3769</v>
       </c>
       <c r="C4">
-        <v>0.3721</v>
+        <v>0.3872</v>
       </c>
     </row>
     <row r="5">
@@ -108,62 +108,62 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.3589</v>
+        <v>0.3588</v>
       </c>
       <c r="C5">
-        <v>0.3639</v>
+        <v>0.3643</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amon-Ra St. Brown</t>
+          <t xml:space="preserve">Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="B6">
-        <v>0.3552</v>
+        <v>0.3585</v>
       </c>
       <c r="C6">
-        <v>0.3528</v>
+        <v>0.3558</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Garrett Wilson</t>
+          <t xml:space="preserve">Kenneth Walker III</t>
         </is>
       </c>
       <c r="B7">
-        <v>0.3002</v>
+        <v>0.3579</v>
       </c>
       <c r="C7">
-        <v>0.3041</v>
+        <v>0.3606</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jahmyr Gibbs</t>
+          <t xml:space="preserve">Travis Kelce</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.2949</v>
+        <v>0.3204</v>
       </c>
       <c r="C8">
-        <v>0.2986</v>
+        <v>0.3168</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Travis Kelce</t>
+          <t xml:space="preserve">Garrett Wilson</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.2783</v>
+        <v>0.2933</v>
       </c>
       <c r="C9">
-        <v>0.2783</v>
+        <v>0.2963</v>
       </c>
     </row>
     <row r="10">
@@ -173,62 +173,62 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.2111</v>
+        <v>0.1989</v>
       </c>
       <c r="C10">
-        <v>0.2123</v>
+        <v>0.2013</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen</t>
+          <t xml:space="preserve">Parker Washington</t>
         </is>
       </c>
       <c r="B11">
-        <v>0.1867</v>
+        <v>0.1961</v>
       </c>
       <c r="C11">
-        <v>0.1883</v>
+        <v>0.1964</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breece Hall</t>
+          <t xml:space="preserve">Josh Allen</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.1853</v>
+        <v>0.1908</v>
       </c>
       <c r="C12">
-        <v>0.1931</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalton Kincaid</t>
+          <t xml:space="preserve">Breece Hall</t>
         </is>
       </c>
       <c r="B13">
-        <v>0.1731</v>
+        <v>0.1892</v>
       </c>
       <c r="C13">
-        <v>0.1725</v>
+        <v>0.1949</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parker Washington</t>
+          <t xml:space="preserve">Dalton Kincaid</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.166</v>
+        <v>0.1828</v>
       </c>
       <c r="C14">
-        <v>0.1628</v>
+        <v>0.1775</v>
       </c>
     </row>
     <row r="15">
@@ -238,23 +238,23 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.1528</v>
+        <v>0.1577</v>
       </c>
       <c r="C15">
-        <v>0.1594</v>
+        <v>0.1644</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonathan Taylor</t>
+          <t xml:space="preserve">Sam LaPorta</t>
         </is>
       </c>
       <c r="B16">
-        <v>0.15</v>
+        <v>0.1185</v>
       </c>
       <c r="C16">
-        <v>0.1549</v>
+        <v>0.1213</v>
       </c>
     </row>
     <row r="17"/>
@@ -350,13 +350,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>49700</v>
+        <v>49900</v>
       </c>
       <c r="C2">
-        <v>162.5363</v>
+        <v>160.3805</v>
       </c>
       <c r="D2">
-        <v>158.8048</v>
+        <v>157.5746</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -365,7 +365,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | De'Von Achane | Garrett Wilson | Parker Washington | Ladd McConkey | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Jaylen Warren | Garrett Wilson | Parker Washington | Tre' Harris | Dalton Schultz | Seahawks</t>
         </is>
       </c>
     </row>
@@ -374,22 +374,22 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>49800</v>
+        <v>49600</v>
       </c>
       <c r="C3">
-        <v>163.4631</v>
+        <v>161.6316</v>
       </c>
       <c r="D3">
-        <v>157.3381</v>
+        <v>155.5882</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALUE_FRONTIER</t>
+          <t xml:space="preserve">BEST_WITH_RB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Jaylen Warren | Garrett Wilson | Ladd McConkey | Tre' Harris | Dalton Schultz | Seahawks</t>
+          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | De'Von Achane | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -398,13 +398,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>50000</v>
+        <v>49800</v>
       </c>
       <c r="C4">
-        <v>163.3098</v>
+        <v>161.9198</v>
       </c>
       <c r="D4">
-        <v>155.7187</v>
+        <v>154.3331</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -413,7 +413,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcus Mariota | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Ladd McConkey | Travis Kelce | Dalton Schultz | Bengals</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Garrett Wilson | Ladd McConkey | Tre' Harris | Travis Kelce | Dalton Schultz | Texans</t>
         </is>
       </c>
     </row>
@@ -422,13 +422,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>49500</v>
+        <v>50000</v>
       </c>
       <c r="C5">
-        <v>162.1901</v>
+        <v>160.7034</v>
       </c>
       <c r="D5">
-        <v>151.855</v>
+        <v>154.6852</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -437,7 +437,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deshaun Watson | Kenneth Walker III | Breece Hall | Jaxon Smith-Njigba | Garrett Wilson | Michael Pittman Jr. | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">C.J. Stroud | Kenneth Walker III | Breece Hall | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -446,22 +446,22 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>49700</v>
+        <v>50000</v>
       </c>
       <c r="C6">
-        <v>162.6074</v>
+        <v>162.0642</v>
       </c>
       <c r="D6">
-        <v>153.5436</v>
+        <v>151.6626</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">BEST_WITH_TE</t>
+          <t xml:space="preserve">VALUE_FRONTIER</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Isaiah Likely | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Patrick Mahomes | Jahmyr Gibbs | Kenneth Walker III | Garrett Wilson | Parker Washington | Jaylin Noel | Travis Kelce | Dalton Schultz | Panthers</t>
         </is>
       </c>
     </row>
@@ -473,10 +473,10 @@
         <v>49800</v>
       </c>
       <c r="C7">
-        <v>162.7914</v>
+        <v>161.0842</v>
       </c>
       <c r="D7">
-        <v>155.0343</v>
+        <v>152.555</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -485,7 +485,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Jaylen Warren | Garrett Wilson | Parker Washington | Tre' Harris | Travis Kelce | Dalton Schultz | Seahawks</t>
+          <t xml:space="preserve">Patrick Mahomes | Jahmyr Gibbs | Kenneth Walker III | Parker Washington | Ladd McConkey | Tre' Harris | Travis Kelce | Dalton Schultz | Bengals</t>
         </is>
       </c>
     </row>
@@ -494,13 +494,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>49700</v>
+        <v>49800</v>
       </c>
       <c r="C8">
-        <v>163.2173</v>
+        <v>160.8528</v>
       </c>
       <c r="D8">
-        <v>149.7265</v>
+        <v>151.2266</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Jahmyr Gibbs | Kenneth Walker III | Garrett Wilson | Tre' Harris | Jaylin Noel | Travis Kelce | Dalton Schultz | Panthers</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Garrett Wilson | Ladd McConkey | Michael Pittman Jr. | Travis Kelce | Dalton Schultz | Titans</t>
         </is>
       </c>
     </row>
@@ -521,10 +521,10 @@
         <v>50000</v>
       </c>
       <c r="C9">
-        <v>162.8921</v>
+        <v>160.9235</v>
       </c>
       <c r="D9">
-        <v>150.2944</v>
+        <v>151.1031</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -533,7 +533,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Parker Washington | Jaylin Noel | Travis Kelce | Dalton Schultz | Seahawks</t>
+          <t xml:space="preserve">Josh Allen | Jahmyr Gibbs | Jaylen Warren | Garrett Wilson | Ladd McConkey | Tre' Harris | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -542,22 +542,22 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>49600</v>
+        <v>49900</v>
       </c>
       <c r="C10">
-        <v>162.7671</v>
+        <v>160.7435</v>
       </c>
       <c r="D10">
-        <v>151.4148</v>
+        <v>155.5758</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">BEST_WITH_QB</t>
+          <t xml:space="preserve">VALUE_FRONTIER</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jared Goff | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Deshaun Watson | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Parker Washington | Travis Kelce | Dalton Schultz | Browns</t>
         </is>
       </c>
     </row>
@@ -566,22 +566,22 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>50000</v>
+        <v>49700</v>
       </c>
       <c r="C11">
-        <v>159.1739</v>
+        <v>159.9127</v>
       </c>
       <c r="D11">
-        <v>150.5445</v>
+        <v>153.1904</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BEST_WITH_RB</t>
+          <t xml:space="preserve">BEST_WITH_QB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Quinshon Judkins | Garrett Wilson | Ladd McConkey | Jaylin Noel | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Jameis Winston | Jahmyr Gibbs | Kenneth Walker III | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -590,22 +590,22 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>50000</v>
+        <v>49900</v>
       </c>
       <c r="C12">
-        <v>161.8097</v>
+        <v>160.7878</v>
       </c>
       <c r="D12">
-        <v>155.6203</v>
+        <v>152.3818</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">BEST_WITH_QB</t>
+          <t xml:space="preserve">VALUE_FRONTIER</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jameis Winston | Kenneth Walker III | Breece Hall | Jaxon Smith-Njigba | Garrett Wilson | Ladd McConkey | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Josh Allen | Breece Hall | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Panthers</t>
         </is>
       </c>
     </row>
@@ -614,13 +614,13 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>49900</v>
+        <v>50000</v>
       </c>
       <c r="C13">
-        <v>162.6742</v>
+        <v>160.3729</v>
       </c>
       <c r="D13">
-        <v>150.9844</v>
+        <v>150.551</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | James Cook III | Garrett Wilson | Parker Washington | Tre' Harris | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Jaxon Smith-Njigba | Ladd McConkey | Tre' Harris | Travis Kelce | Dalton Schultz | Jaguars</t>
         </is>
       </c>
     </row>
@@ -641,10 +641,10 @@
         <v>50000</v>
       </c>
       <c r="C14">
-        <v>162.6667</v>
+        <v>160.802</v>
       </c>
       <c r="D14">
-        <v>150.5654</v>
+        <v>152.0121</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Parker Washington | Ladd McConkey | Michael Pittman Jr. | Travis Kelce | Dalton Schultz | Bengals</t>
+          <t xml:space="preserve">Deshaun Watson | Jahmyr Gibbs | Kenneth Walker III | Breece Hall | Garrett Wilson | Ladd McConkey | Jaylin Noel | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -665,19 +665,19 @@
         <v>50000</v>
       </c>
       <c r="C15">
-        <v>162.3385</v>
+        <v>160.0912</v>
       </c>
       <c r="D15">
-        <v>150.4268</v>
+        <v>152.9676</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALUE_FRONTIER</t>
+          <t xml:space="preserve">BEST_WITH_TE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Jaylen Warren | Rashee Rice | Garrett Wilson | Michael Pittman Jr. | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Dalton Schultz | Hunter Henry | Seahawks</t>
         </is>
       </c>
     </row>
@@ -686,13 +686,13 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>50000</v>
+        <v>49900</v>
       </c>
       <c r="C16">
-        <v>162.9604</v>
+        <v>160.9309</v>
       </c>
       <c r="D16">
-        <v>151.6086</v>
+        <v>147.9515</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Jaylin Noel | Travis Kelce | Dalton Schultz | Titans</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Michael Pittman Jr. | Tre' Harris | Travis Kelce | Dalton Schultz | Jaguars</t>
         </is>
       </c>
     </row>
@@ -710,13 +710,13 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>49800</v>
+        <v>50000</v>
       </c>
       <c r="C17">
-        <v>162.8204</v>
+        <v>160.4449</v>
       </c>
       <c r="D17">
-        <v>152.8991</v>
+        <v>150.4551</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Jahmyr Gibbs | Kenneth Walker III | Breece Hall | Garrett Wilson | Tre' Harris | Jaylin Noel | Dalton Schultz | Panthers</t>
+          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Jaxon Smith-Njigba | Garrett Wilson | Tre' Harris | Sam LaPorta | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -734,13 +734,13 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>49700</v>
+        <v>50000</v>
       </c>
       <c r="C18">
-        <v>162.5353</v>
+        <v>158.4838</v>
       </c>
       <c r="D18">
-        <v>153.6231</v>
+        <v>143.3149</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Chase Brown | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Patrick Mahomes | Jonathan Taylor | Kenneth Walker III | Amon-Ra St. Brown | Ladd McConkey | Jaylin Noel | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>49900</v>
+        <v>50000</v>
       </c>
       <c r="C19">
-        <v>162.4472</v>
+        <v>159.621</v>
       </c>
       <c r="D19">
-        <v>153.469</v>
+        <v>147.3436</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALUE_FRONTIER</t>
+          <t xml:space="preserve">BEST_WITH_TE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deshaun Watson | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Michael Pittman Jr. | Travis Kelce | Dalton Schultz | Seahawks</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Garrett Wilson | Ladd McConkey | Jaylin Noel | Dalton Kincaid | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -782,13 +782,13 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>50000</v>
+        <v>49800</v>
       </c>
       <c r="C20">
-        <v>162.2927</v>
+        <v>160.6504</v>
       </c>
       <c r="D20">
-        <v>154.1282</v>
+        <v>146.8705</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Dalton Schultz | Hunter Henry | Seahawks</t>
+          <t xml:space="preserve">Patrick Mahomes | Jahmyr Gibbs | Breece Hall | Garrett Wilson | Parker Washington | Michael Pittman Jr. | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -806,22 +806,22 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>49900</v>
+        <v>50000</v>
       </c>
       <c r="C21">
-        <v>162.1768</v>
+        <v>159.8654</v>
       </c>
       <c r="D21">
-        <v>150.1345</v>
+        <v>151.7472</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALUE_FRONTIER</t>
+          <t xml:space="preserve">BEST_WITH_WR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Jaylen Warren | Parker Washington | Ladd McConkey | Jaylin Noel | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Romeo Doubs | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -830,13 +830,13 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>50000</v>
+        <v>49600</v>
       </c>
       <c r="C22">
-        <v>164.1895</v>
+        <v>162.0308</v>
       </c>
       <c r="D22">
-        <v>154.3442</v>
+        <v>156.1281</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Jahmyr Gibbs | Kenneth Walker III | Garrett Wilson | Parker Washington | Tre' Harris | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Garrett Wilson | Parker Washington | Tre' Harris | Travis Kelce | Dalton Schultz | Jaguars</t>
         </is>
       </c>
     </row>
@@ -854,13 +854,13 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>49800</v>
+        <v>50000</v>
       </c>
       <c r="C23">
-        <v>163.0641</v>
+        <v>161.187</v>
       </c>
       <c r="D23">
-        <v>152.6097</v>
+        <v>155.0313</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Michael Pittman Jr. | Travis Kelce | Dalton Schultz | Bengals</t>
+          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Jaylen Warren | Garrett Wilson | Parker Washington | Ladd McConkey | Travis Kelce | Dalton Schultz | Seahawks</t>
         </is>
       </c>
     </row>
@@ -881,10 +881,10 @@
         <v>50000</v>
       </c>
       <c r="C24">
-        <v>162.8801</v>
+        <v>160.6156</v>
       </c>
       <c r="D24">
-        <v>148.4065</v>
+        <v>154.5692</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Garrett Wilson | Ladd McConkey | Jaylin Noel | Dalton Kincaid | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">C.J. Stroud | Kenneth Walker III | Breece Hall | Garrett Wilson | Parker Washington | Ladd McConkey | Travis Kelce | Dalton Schultz | Seahawks</t>
         </is>
       </c>
     </row>
@@ -902,13 +902,13 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>49800</v>
+        <v>50000</v>
       </c>
       <c r="C25">
-        <v>162.5717</v>
+        <v>160.3564</v>
       </c>
       <c r="D25">
-        <v>153.3608</v>
+        <v>145.7147</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">C.J. Stroud | Kenneth Walker III | Breece Hall | Jaxon Smith-Njigba | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Panthers</t>
+          <t xml:space="preserve">Deshaun Watson | Kenneth Walker III | Breece Hall | Jaxon Smith-Njigba | Amon-Ra St. Brown | Jaylin Noel | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -926,22 +926,22 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>49800</v>
+        <v>50000</v>
       </c>
       <c r="C26">
-        <v>162.495</v>
+        <v>160.095</v>
       </c>
       <c r="D26">
-        <v>151.2777</v>
+        <v>152.2921</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALUE_FRONTIER</t>
+          <t xml:space="preserve">BEST_WITH_WR</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Jahmyr Gibbs | Kenneth Walker III | Garrett Wilson | Ladd McConkey | Jaylin Noel | Travis Kelce | Dalton Schultz | Jaguars</t>
+          <t xml:space="preserve">Patrick Mahomes | Jahmyr Gibbs | Kenneth Walker III | Garrett Wilson | Tetairoa McMillan | Tre' Harris | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -950,13 +950,13 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>50000</v>
+        <v>49800</v>
       </c>
       <c r="C27">
-        <v>162.1987</v>
+        <v>161.8645</v>
       </c>
       <c r="D27">
-        <v>146.7805</v>
+        <v>150.3276</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Rashee Rice | Garrett Wilson | Tre' Harris | Jaylin Noel | Dalton Schultz | Seahawks</t>
+          <t xml:space="preserve">Patrick Mahomes | Jahmyr Gibbs | Kenneth Walker III | Garrett Wilson | Ladd McConkey | Jaylin Noel | Travis Kelce | Dalton Schultz | Bengals</t>
         </is>
       </c>
     </row>
@@ -977,19 +977,19 @@
         <v>50000</v>
       </c>
       <c r="C28">
-        <v>162.5502</v>
+        <v>161.5618</v>
       </c>
       <c r="D28">
-        <v>149.0815</v>
+        <v>148.019</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">BEST_WITH_RB</t>
+          <t xml:space="preserve">VALUE_FRONTIER</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Rhamondre Stevenson | Amon-Ra St. Brown | Garrett Wilson | Jaylin Noel | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Jaylen Warren | Amon-Ra St. Brown | Parker Washington | Jaylin Noel | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -1001,10 +1001,10 @@
         <v>49900</v>
       </c>
       <c r="C29">
-        <v>163.7737</v>
+        <v>160.954</v>
       </c>
       <c r="D29">
-        <v>151.7581</v>
+        <v>145.3573</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Jaxon Smith-Njigba | Parker Washington | Tre' Harris | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Patrick Mahomes | Jahmyr Gibbs | Kenneth Walker III | Jaxon Smith-Njigba | Tre' Harris | Jaylin Noel | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -1022,13 +1022,13 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>49500</v>
+        <v>50000</v>
       </c>
       <c r="C30">
-        <v>162.5956</v>
+        <v>160.8618</v>
       </c>
       <c r="D30">
-        <v>147.2054</v>
+        <v>149.4332</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Jaxon Smith-Njigba | Tre' Harris | Jaylin Noel | Travis Kelce | Dalton Schultz | Bengals</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Parker Washington | Ladd McConkey | Michael Pittman Jr. | Travis Kelce | Dalton Schultz | Bengals</t>
         </is>
       </c>
     </row>
@@ -1046,13 +1046,13 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>49900</v>
+        <v>50000</v>
       </c>
       <c r="C31">
-        <v>162.3945</v>
+        <v>160.6238</v>
       </c>
       <c r="D31">
-        <v>158.207</v>
+        <v>147.9297</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Jaylen Warren | Garrett Wilson | Parker Washington | Tre' Harris | Dalton Schultz | Seahawks</t>
+          <t xml:space="preserve">C.J. Stroud | Jahmyr Gibbs | Kenneth Walker III | Garrett Wilson | Ladd McConkey | Michael Pittman Jr. | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -1073,10 +1073,10 @@
         <v>49700</v>
       </c>
       <c r="C32">
-        <v>162.3658</v>
+        <v>160.6028</v>
       </c>
       <c r="D32">
-        <v>153.4258</v>
+        <v>151.7811</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">C.J. Stroud | Kenneth Walker III | Breece Hall | Jaxon Smith-Njigba | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Bengals</t>
+          <t xml:space="preserve">Josh Allen | Breece Hall | Jaylen Warren | Garrett Wilson | Parker Washington | Ladd McConkey | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -1094,13 +1094,13 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>49900</v>
+        <v>49800</v>
       </c>
       <c r="C33">
-        <v>162.2794</v>
+        <v>160.5819</v>
       </c>
       <c r="D33">
-        <v>154.1558</v>
+        <v>152.3193</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Jaylen Warren | Garrett Wilson | Ladd McConkey | Jaylin Noel | Dalton Schultz | Titans</t>
+          <t xml:space="preserve">Josh Allen | Breece Hall | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Bengals</t>
         </is>
       </c>
     </row>
@@ -1118,22 +1118,22 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>50000</v>
+        <v>49500</v>
       </c>
       <c r="C34">
-        <v>160.7397</v>
+        <v>160.553</v>
       </c>
       <c r="D34">
-        <v>153.1707</v>
+        <v>146.5198</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">BEST_WITH_QB</t>
+          <t xml:space="preserve">VALUE_FRONTIER</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sam Darnold | Kenneth Walker III | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Ladd McConkey | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Josh Allen | Jahmyr Gibbs | Breece Hall | Garrett Wilson | Michael Pittman Jr. | Tre' Harris | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -1142,22 +1142,22 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>49700</v>
+        <v>49600</v>
       </c>
       <c r="C35">
-        <v>158.6256</v>
+        <v>162.798</v>
       </c>
       <c r="D35">
-        <v>151.0406</v>
+        <v>156.5606</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">BEST_WITH_QB</t>
+          <t xml:space="preserve">VALUE_FRONTIER</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aaron Rodgers | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Ladd McConkey | Tre' Harris | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Garrett Wilson | Parker Washington | Tre' Harris | Travis Kelce | Dalton Schultz | Bengals</t>
         </is>
       </c>
     </row>
@@ -1166,22 +1166,22 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>50000</v>
+        <v>49500</v>
       </c>
       <c r="C36">
-        <v>162.0446</v>
+        <v>162.586</v>
       </c>
       <c r="D36">
-        <v>152.4128</v>
+        <v>150.0189</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">BEST_WITH_DST</t>
+          <t xml:space="preserve">VALUE_FRONTIER</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Garrett Wilson | Ladd McConkey | Jaylin Noel | Travis Kelce | Dalton Schultz | Chiefs</t>
+          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Jaylin Noel | Travis Kelce | Dalton Schultz | Panthers</t>
         </is>
       </c>
     </row>
@@ -1190,13 +1190,13 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>49700</v>
+        <v>50000</v>
       </c>
       <c r="C37">
-        <v>165.0051</v>
+        <v>162.3068</v>
       </c>
       <c r="D37">
-        <v>155.1735</v>
+        <v>151.4813</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Jaguars</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Rashee Rice | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Bengals</t>
         </is>
       </c>
     </row>
@@ -1217,10 +1217,10 @@
         <v>49500</v>
       </c>
       <c r="C38">
-        <v>164.8395</v>
+        <v>162.2817</v>
       </c>
       <c r="D38">
-        <v>152.5408</v>
+        <v>152.7547</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Jaylin Noel | Travis Kelce | Dalton Schultz | Panthers</t>
+          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Patriots</t>
         </is>
       </c>
     </row>
@@ -1238,13 +1238,13 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>50000</v>
+        <v>49900</v>
       </c>
       <c r="C39">
-        <v>164.1484</v>
+        <v>162.0233</v>
       </c>
       <c r="D39">
-        <v>155.292</v>
+        <v>153.9821</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Jaxon Smith-Njigba | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Browns</t>
+          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Seahawks</t>
         </is>
       </c>
     </row>
@@ -1262,13 +1262,13 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>50000</v>
+        <v>49700</v>
       </c>
       <c r="C40">
-        <v>163.9745</v>
+        <v>161.9668</v>
       </c>
       <c r="D40">
-        <v>148.2609</v>
+        <v>151.3119</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Michael Pittman Jr. | Tre' Harris | Travis Kelce | Dalton Schultz | Panthers</t>
+          <t xml:space="preserve">Josh Allen | Jahmyr Gibbs | Kenneth Walker III | Garrett Wilson | Tre' Harris | Jaylin Noel | Travis Kelce | Dalton Schultz | Panthers</t>
         </is>
       </c>
     </row>
@@ -1286,13 +1286,13 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>49600</v>
+        <v>49900</v>
       </c>
       <c r="C41">
-        <v>163.9213</v>
+        <v>161.7661</v>
       </c>
       <c r="D41">
-        <v>151.2197</v>
+        <v>153.1259</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Michael Pittman Jr. | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Patrick Mahomes | Jahmyr Gibbs | Kenneth Walker III | Garrett Wilson | Ladd McConkey | Tre' Harris | Travis Kelce | Dalton Schultz | Patriots</t>
         </is>
       </c>
     </row>
@@ -1310,13 +1310,13 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>50000</v>
+        <v>49900</v>
       </c>
       <c r="C42">
-        <v>163.9106</v>
+        <v>161.7567</v>
       </c>
       <c r="D42">
-        <v>153.8223</v>
+        <v>153.9868</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Michael Pittman Jr. | Travis Kelce | Dalton Schultz | Titans</t>
+          <t xml:space="preserve">Marcus Mariota | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Parker Washington | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -1334,13 +1334,13 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>49400</v>
+        <v>49900</v>
       </c>
       <c r="C43">
-        <v>163.6372</v>
+        <v>161.6981</v>
       </c>
       <c r="D43">
-        <v>150.5943</v>
+        <v>148.384</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Jaylen Warren | Garrett Wilson | Ladd McConkey | Michael Pittman Jr. | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Michael Pittman Jr. | Tre' Harris | Travis Kelce | Dalton Schultz | Bengals</t>
         </is>
       </c>
     </row>
@@ -1358,13 +1358,13 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>50000</v>
+        <v>49800</v>
       </c>
       <c r="C44">
-        <v>163.5295</v>
+        <v>161.5427</v>
       </c>
       <c r="D44">
-        <v>149.8911</v>
+        <v>149.8101</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Jaylen Warren | Amon-Ra St. Brown | Ladd McConkey | Jaylin Noel | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Patrick Mahomes | Breece Hall | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Ladd McConkey | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -1382,13 +1382,13 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>49800</v>
+        <v>49900</v>
       </c>
       <c r="C45">
-        <v>163.5239</v>
+        <v>161.5365</v>
       </c>
       <c r="D45">
-        <v>149.1754</v>
+        <v>151.0826</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Parker Washington | Ladd McConkey | Michael Pittman Jr. | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Patrick Mahomes | Breece Hall | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Parker Washington | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -1406,13 +1406,13 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>50000</v>
+        <v>49200</v>
       </c>
       <c r="C46">
-        <v>163.2179</v>
+        <v>161.4464</v>
       </c>
       <c r="D46">
-        <v>151.7693</v>
+        <v>150.6548</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Jaxon Smith-Njigba | Ladd McConkey | Tre' Harris | Travis Kelce | Dalton Schultz | Jaguars</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Garrett Wilson | Ladd McConkey | Jaylin Noel | Travis Kelce | Dalton Schultz | Bengals</t>
         </is>
       </c>
     </row>
@@ -1430,13 +1430,13 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>49600</v>
+        <v>49900</v>
       </c>
       <c r="C47">
-        <v>162.6831</v>
+        <v>161.2901</v>
       </c>
       <c r="D47">
-        <v>149.135</v>
+        <v>152.6175</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Breece Hall | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Patrick Mahomes | Jahmyr Gibbs | Kenneth Walker III | Parker Washington | Ladd McConkey | Tre' Harris | Travis Kelce | Dalton Schultz | Panthers</t>
         </is>
       </c>
     </row>
@@ -1454,13 +1454,13 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>49800</v>
+        <v>49900</v>
       </c>
       <c r="C48">
-        <v>162.608</v>
+        <v>161.1249</v>
       </c>
       <c r="D48">
-        <v>149.669</v>
+        <v>154.0495</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Parker Washington | Ladd McConkey | Jaylin Noel | Travis Kelce | Dalton Schultz | Seahawks</t>
+          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Jaxon Smith-Njigba | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Titans</t>
         </is>
       </c>
     </row>
@@ -1478,13 +1478,13 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>50000</v>
+        <v>49800</v>
       </c>
       <c r="C49">
-        <v>162.5412</v>
+        <v>161.0834</v>
       </c>
       <c r="D49">
-        <v>152.8313</v>
+        <v>155.953</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Jets</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Jaylen Warren | Garrett Wilson | Parker Washington | Tre' Harris | Travis Kelce | Dalton Schultz | Seahawks</t>
         </is>
       </c>
     </row>
@@ -1555,13 +1555,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.4775</v>
+        <v>0.5</v>
       </c>
       <c r="C2">
-        <v>164.7832</v>
+        <v>162.7486</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E2">
         <v>1.0</v>
@@ -1574,13 +1574,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.7575</v>
+        <v>0.77</v>
       </c>
       <c r="C3">
-        <v>162.7496</v>
+        <v>161.0701</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E3">
         <v>1.0</v>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.9025</v>
+        <v>0.8875</v>
       </c>
       <c r="C6">
-        <v>0.7175</v>
+        <v>0.7225</v>
       </c>
       <c r="D6">
         <v>0.4792</v>
@@ -1623,13 +1623,13 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.7175</v>
+        <v>0.7025</v>
       </c>
       <c r="C7">
-        <v>0.4025</v>
+        <v>0.3625</v>
       </c>
       <c r="D7">
-        <v>0.5208</v>
+        <v>0.5</v>
       </c>
       <c r="E7"/>
     </row>
@@ -1640,13 +1640,13 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.8575</v>
+        <v>0.8775</v>
       </c>
       <c r="C8">
-        <v>0.605</v>
+        <v>0.635</v>
       </c>
       <c r="D8">
-        <v>0.4583</v>
+        <v>0.5833</v>
       </c>
       <c r="E8"/>
     </row>
@@ -1657,13 +1657,13 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.755</v>
+        <v>0.73</v>
       </c>
       <c r="C9">
-        <v>0.49</v>
+        <v>0.4975</v>
       </c>
       <c r="D9">
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
       <c r="E9"/>
     </row>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>2.91</v>
+        <v>12.67</v>
       </c>
       <c r="E2">
         <v>336</v>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>2.79</v>
+        <v>12.55</v>
       </c>
       <c r="E3">
         <v>336</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>2.77</v>
+        <v>12.53</v>
       </c>
       <c r="E4">
         <v>336</v>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>2.73</v>
+        <v>12.49</v>
       </c>
       <c r="E5">
         <v>720</v>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.98</v>
+        <v>10.74</v>
       </c>
       <c r="E6">
         <v>336</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>1.16</v>
+        <v>10.93</v>
       </c>
       <c r="E7">
         <v>336</v>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.95</v>
+        <v>10.71</v>
       </c>
       <c r="E8">
         <v>336</v>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.84</v>
+        <v>10.61</v>
       </c>
       <c r="E9">
         <v>336</v>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>1.22</v>
+        <v>10.98</v>
       </c>
       <c r="E10">
         <v>720</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.92</v>
+        <v>0.49</v>
       </c>
       <c r="E11">
         <v>168</v>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="D12">
-        <v>2.19</v>
+        <v>0.15</v>
       </c>
       <c r="E12">
         <v>36</v>
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="D13">
-        <v>11.85</v>
+        <v>21.61</v>
       </c>
       <c r="E13">
         <v>6</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="D14">
-        <v>1.26</v>
+        <v>0.04</v>
       </c>
       <c r="E14">
         <v>36</v>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.33</v>
+        <v>0.01</v>
       </c>
       <c r="E15">
         <v>24</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>1790569118</v>
+        <v>1790604240</v>
       </c>
     </row>
     <row r="7">

--- a/nfl/dfs/salaries/DK_WEEK3_DELIVERABLE_SUPPLEMENT.xlsx
+++ b/nfl/dfs/salaries/DK_WEEK3_DELIVERABLE_SUPPLEMENT.xlsx
@@ -356,7 +356,7 @@
         <v>160.3805</v>
       </c>
       <c r="D2">
-        <v>157.5746</v>
+        <v>158.3696</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -380,7 +380,7 @@
         <v>161.6316</v>
       </c>
       <c r="D3">
-        <v>155.5882</v>
+        <v>156.2432</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -401,10 +401,10 @@
         <v>49800</v>
       </c>
       <c r="C4">
-        <v>161.9198</v>
+        <v>160.8528</v>
       </c>
       <c r="D4">
-        <v>154.3331</v>
+        <v>152.0366</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -413,7 +413,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Garrett Wilson | Ladd McConkey | Tre' Harris | Travis Kelce | Dalton Schultz | Texans</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Garrett Wilson | Ladd McConkey | Michael Pittman Jr. | Travis Kelce | Dalton Schultz | Titans</t>
         </is>
       </c>
     </row>
@@ -425,10 +425,10 @@
         <v>50000</v>
       </c>
       <c r="C5">
-        <v>160.7034</v>
+        <v>162.0642</v>
       </c>
       <c r="D5">
-        <v>154.6852</v>
+        <v>152.4076</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -437,7 +437,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">C.J. Stroud | Kenneth Walker III | Breece Hall | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Patrick Mahomes | Jahmyr Gibbs | Kenneth Walker III | Garrett Wilson | Parker Washington | Jaylin Noel | Travis Kelce | Dalton Schultz | Panthers</t>
         </is>
       </c>
     </row>
@@ -449,10 +449,10 @@
         <v>50000</v>
       </c>
       <c r="C6">
-        <v>162.0642</v>
+        <v>160.7034</v>
       </c>
       <c r="D6">
-        <v>151.6626</v>
+        <v>155.3402</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Jahmyr Gibbs | Kenneth Walker III | Garrett Wilson | Parker Washington | Jaylin Noel | Travis Kelce | Dalton Schultz | Panthers</t>
+          <t xml:space="preserve">C.J. Stroud | Kenneth Walker III | Breece Hall | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
         <v>161.0842</v>
       </c>
       <c r="D7">
-        <v>152.555</v>
+        <v>153.45</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -494,13 +494,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>49800</v>
+        <v>50000</v>
       </c>
       <c r="C8">
-        <v>160.8528</v>
+        <v>161.1685</v>
       </c>
       <c r="D8">
-        <v>151.2266</v>
+        <v>154.2233</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Garrett Wilson | Ladd McConkey | Michael Pittman Jr. | Travis Kelce | Dalton Schultz | Titans</t>
+          <t xml:space="preserve">Deshaun Watson | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Ladd McConkey | Travis Kelce | Dalton Schultz | Patriots</t>
         </is>
       </c>
     </row>
@@ -518,22 +518,22 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>50000</v>
+        <v>49700</v>
       </c>
       <c r="C9">
-        <v>160.9235</v>
+        <v>159.9127</v>
       </c>
       <c r="D9">
-        <v>151.1031</v>
+        <v>153.8454</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALUE_FRONTIER</t>
+          <t xml:space="preserve">BEST_WITH_QB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Jahmyr Gibbs | Jaylen Warren | Garrett Wilson | Ladd McConkey | Tre' Harris | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Jameis Winston | Jahmyr Gibbs | Kenneth Walker III | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -542,13 +542,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>49900</v>
+        <v>49700</v>
       </c>
       <c r="C10">
-        <v>160.7435</v>
+        <v>161.0896</v>
       </c>
       <c r="D10">
-        <v>155.5758</v>
+        <v>155.4755</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deshaun Watson | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Parker Washington | Travis Kelce | Dalton Schultz | Browns</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Jaylen Warren | Garrett Wilson | Ladd McConkey | Tre' Harris | Travis Kelce | Dalton Schultz | Seahawks</t>
         </is>
       </c>
     </row>
@@ -566,22 +566,22 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>49700</v>
+        <v>50000</v>
       </c>
       <c r="C11">
-        <v>159.9127</v>
+        <v>160.3729</v>
       </c>
       <c r="D11">
-        <v>153.1904</v>
+        <v>151.266</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BEST_WITH_QB</t>
+          <t xml:space="preserve">VALUE_FRONTIER</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jameis Winston | Jahmyr Gibbs | Kenneth Walker III | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Jaxon Smith-Njigba | Ladd McConkey | Tre' Harris | Travis Kelce | Dalton Schultz | Jaguars</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
         <v>160.7878</v>
       </c>
       <c r="D12">
-        <v>152.3818</v>
+        <v>153.1268</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>50000</v>
+        <v>49600</v>
       </c>
       <c r="C13">
-        <v>160.3729</v>
+        <v>160.9937</v>
       </c>
       <c r="D13">
-        <v>150.551</v>
+        <v>151.5319</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Jaxon Smith-Njigba | Ladd McConkey | Tre' Harris | Travis Kelce | Dalton Schultz | Jaguars</t>
+          <t xml:space="preserve">Josh Allen | Jahmyr Gibbs | Kenneth Walker III | Garrett Wilson | Tre' Harris | Jaylin Noel | Travis Kelce | Dalton Schultz | Jaguars</t>
         </is>
       </c>
     </row>
@@ -638,13 +638,13 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>50000</v>
+        <v>49900</v>
       </c>
       <c r="C14">
-        <v>160.802</v>
+        <v>161.9911</v>
       </c>
       <c r="D14">
-        <v>152.0121</v>
+        <v>151.3236</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deshaun Watson | Jahmyr Gibbs | Kenneth Walker III | Breece Hall | Garrett Wilson | Ladd McConkey | Jaylin Noel | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Jaxon Smith-Njigba | Parker Washington | Tre' Harris | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -662,22 +662,22 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>50000</v>
+        <v>49800</v>
       </c>
       <c r="C15">
-        <v>160.0912</v>
+        <v>161.8645</v>
       </c>
       <c r="D15">
-        <v>152.9676</v>
+        <v>151.2226</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">BEST_WITH_TE</t>
+          <t xml:space="preserve">VALUE_FRONTIER</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Dalton Schultz | Hunter Henry | Seahawks</t>
+          <t xml:space="preserve">Patrick Mahomes | Jahmyr Gibbs | Kenneth Walker III | Garrett Wilson | Ladd McConkey | Jaylin Noel | Travis Kelce | Dalton Schultz | Bengals</t>
         </is>
       </c>
     </row>
@@ -686,13 +686,13 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>49900</v>
+        <v>50000</v>
       </c>
       <c r="C16">
-        <v>160.9309</v>
+        <v>160.4449</v>
       </c>
       <c r="D16">
-        <v>147.9515</v>
+        <v>151.1101</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Michael Pittman Jr. | Tre' Harris | Travis Kelce | Dalton Schultz | Jaguars</t>
+          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Jaxon Smith-Njigba | Garrett Wilson | Tre' Harris | Sam LaPorta | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -713,10 +713,10 @@
         <v>50000</v>
       </c>
       <c r="C17">
-        <v>160.4449</v>
+        <v>160.3564</v>
       </c>
       <c r="D17">
-        <v>150.4551</v>
+        <v>146.3697</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Jaxon Smith-Njigba | Garrett Wilson | Tre' Harris | Sam LaPorta | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Deshaun Watson | Kenneth Walker III | Breece Hall | Jaxon Smith-Njigba | Amon-Ra St. Brown | Jaylin Noel | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -737,19 +737,19 @@
         <v>50000</v>
       </c>
       <c r="C18">
-        <v>158.4838</v>
+        <v>160.0912</v>
       </c>
       <c r="D18">
-        <v>143.3149</v>
+        <v>153.7626</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">BEST_WITH_RB</t>
+          <t xml:space="preserve">BEST_WITH_TE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Jonathan Taylor | Kenneth Walker III | Amon-Ra St. Brown | Ladd McConkey | Jaylin Noel | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Dalton Schultz | Hunter Henry | Seahawks</t>
         </is>
       </c>
     </row>
@@ -761,19 +761,19 @@
         <v>50000</v>
       </c>
       <c r="C19">
-        <v>159.621</v>
+        <v>159.1415</v>
       </c>
       <c r="D19">
-        <v>147.3436</v>
+        <v>151.9623</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">BEST_WITH_TE</t>
+          <t xml:space="preserve">BEST_WITH_DST</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Garrett Wilson | Ladd McConkey | Jaylin Noel | Dalton Kincaid | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Garrett Wilson | Ladd McConkey | Jaylin Noel | Travis Kelce | Dalton Schultz | Chiefs</t>
         </is>
       </c>
     </row>
@@ -782,13 +782,13 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>49800</v>
+        <v>50000</v>
       </c>
       <c r="C20">
-        <v>160.6504</v>
+        <v>160.9235</v>
       </c>
       <c r="D20">
-        <v>146.8705</v>
+        <v>151.7581</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Jahmyr Gibbs | Breece Hall | Garrett Wilson | Parker Washington | Michael Pittman Jr. | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Josh Allen | Jahmyr Gibbs | Jaylen Warren | Garrett Wilson | Ladd McConkey | Tre' Harris | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -806,22 +806,22 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>50000</v>
+        <v>49900</v>
       </c>
       <c r="C21">
-        <v>159.8654</v>
+        <v>161.157</v>
       </c>
       <c r="D21">
-        <v>151.7472</v>
+        <v>152.0901</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">BEST_WITH_WR</t>
+          <t xml:space="preserve">BEST_WITH_QB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Romeo Doubs | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Malik Willis | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Parker Washington | Ladd McConkey | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -830,22 +830,22 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>49600</v>
+        <v>50000</v>
       </c>
       <c r="C22">
-        <v>162.0308</v>
+        <v>159.8654</v>
       </c>
       <c r="D22">
-        <v>156.1281</v>
+        <v>152.4022</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALUE_FRONTIER</t>
+          <t xml:space="preserve">BEST_WITH_WR</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Garrett Wilson | Parker Washington | Tre' Harris | Travis Kelce | Dalton Schultz | Jaguars</t>
+          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Romeo Doubs | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -857,10 +857,10 @@
         <v>50000</v>
       </c>
       <c r="C23">
-        <v>161.187</v>
+        <v>162.3068</v>
       </c>
       <c r="D23">
-        <v>155.0313</v>
+        <v>152.3763</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Jaylen Warren | Garrett Wilson | Parker Washington | Ladd McConkey | Travis Kelce | Dalton Schultz | Seahawks</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Rashee Rice | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Bengals</t>
         </is>
       </c>
     </row>
@@ -878,13 +878,13 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>50000</v>
+        <v>49200</v>
       </c>
       <c r="C24">
-        <v>160.6156</v>
+        <v>161.4464</v>
       </c>
       <c r="D24">
-        <v>154.5692</v>
+        <v>151.5498</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">C.J. Stroud | Kenneth Walker III | Breece Hall | Garrett Wilson | Parker Washington | Ladd McConkey | Travis Kelce | Dalton Schultz | Seahawks</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Garrett Wilson | Ladd McConkey | Jaylin Noel | Travis Kelce | Dalton Schultz | Bengals</t>
         </is>
       </c>
     </row>
@@ -905,10 +905,10 @@
         <v>50000</v>
       </c>
       <c r="C25">
-        <v>160.3564</v>
+        <v>161.1187</v>
       </c>
       <c r="D25">
-        <v>145.7147</v>
+        <v>153.0067</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deshaun Watson | Kenneth Walker III | Breece Hall | Jaxon Smith-Njigba | Amon-Ra St. Brown | Jaylin Noel | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Garrett Wilson | Parker Washington | Michael Pittman Jr. | Travis Kelce | Dalton Schultz | Browns</t>
         </is>
       </c>
     </row>
@@ -926,22 +926,22 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>50000</v>
+        <v>49800</v>
       </c>
       <c r="C26">
-        <v>160.095</v>
+        <v>161.0834</v>
       </c>
       <c r="D26">
-        <v>152.2921</v>
+        <v>156.748</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">BEST_WITH_WR</t>
+          <t xml:space="preserve">VALUE_FRONTIER</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Jahmyr Gibbs | Kenneth Walker III | Garrett Wilson | Tetairoa McMillan | Tre' Harris | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Jaylen Warren | Garrett Wilson | Parker Washington | Tre' Harris | Travis Kelce | Dalton Schultz | Seahawks</t>
         </is>
       </c>
     </row>
@@ -950,13 +950,13 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>49800</v>
+        <v>49900</v>
       </c>
       <c r="C27">
-        <v>161.8645</v>
+        <v>160.9309</v>
       </c>
       <c r="D27">
-        <v>150.3276</v>
+        <v>148.6665</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Jahmyr Gibbs | Kenneth Walker III | Garrett Wilson | Ladd McConkey | Jaylin Noel | Travis Kelce | Dalton Schultz | Bengals</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Michael Pittman Jr. | Tre' Harris | Travis Kelce | Dalton Schultz | Jaguars</t>
         </is>
       </c>
     </row>
@@ -974,13 +974,13 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>50000</v>
+        <v>49500</v>
       </c>
       <c r="C28">
-        <v>161.5618</v>
+        <v>160.5379</v>
       </c>
       <c r="D28">
-        <v>148.019</v>
+        <v>154.2229</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Jaylen Warren | Amon-Ra St. Brown | Parker Washington | Jaylin Noel | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Deshaun Watson | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Parker Washington | Tre' Harris | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -998,13 +998,13 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>49900</v>
+        <v>49700</v>
       </c>
       <c r="C29">
-        <v>160.954</v>
+        <v>162.9707</v>
       </c>
       <c r="D29">
-        <v>145.3573</v>
+        <v>154.8722</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Jahmyr Gibbs | Kenneth Walker III | Jaxon Smith-Njigba | Tre' Harris | Jaylin Noel | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Jaguars</t>
         </is>
       </c>
     </row>
@@ -1022,13 +1022,13 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>50000</v>
+        <v>49900</v>
       </c>
       <c r="C30">
-        <v>160.8618</v>
+        <v>161.5365</v>
       </c>
       <c r="D30">
-        <v>149.4332</v>
+        <v>151.7376</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Parker Washington | Ladd McConkey | Michael Pittman Jr. | Travis Kelce | Dalton Schultz | Bengals</t>
+          <t xml:space="preserve">Patrick Mahomes | Breece Hall | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Parker Washington | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -1049,10 +1049,10 @@
         <v>50000</v>
       </c>
       <c r="C31">
-        <v>160.6238</v>
+        <v>161.187</v>
       </c>
       <c r="D31">
-        <v>147.9297</v>
+        <v>155.8263</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">C.J. Stroud | Jahmyr Gibbs | Kenneth Walker III | Garrett Wilson | Ladd McConkey | Michael Pittman Jr. | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Jaylen Warren | Garrett Wilson | Parker Washington | Ladd McConkey | Travis Kelce | Dalton Schultz | Seahawks</t>
         </is>
       </c>
     </row>
@@ -1070,13 +1070,13 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>49700</v>
+        <v>49900</v>
       </c>
       <c r="C32">
-        <v>160.6028</v>
+        <v>161.1249</v>
       </c>
       <c r="D32">
-        <v>151.7811</v>
+        <v>154.8595</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Breece Hall | Jaylen Warren | Garrett Wilson | Parker Washington | Ladd McConkey | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Jaxon Smith-Njigba | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Titans</t>
         </is>
       </c>
     </row>
@@ -1094,13 +1094,13 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>49800</v>
+        <v>50000</v>
       </c>
       <c r="C33">
-        <v>160.5819</v>
+        <v>160.6238</v>
       </c>
       <c r="D33">
-        <v>152.3193</v>
+        <v>148.5847</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Breece Hall | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Bengals</t>
+          <t xml:space="preserve">C.J. Stroud | Jahmyr Gibbs | Kenneth Walker III | Garrett Wilson | Ladd McConkey | Michael Pittman Jr. | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -1118,13 +1118,13 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>49500</v>
+        <v>50000</v>
       </c>
       <c r="C34">
-        <v>160.553</v>
+        <v>160.6156</v>
       </c>
       <c r="D34">
-        <v>146.5198</v>
+        <v>155.3642</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Jahmyr Gibbs | Breece Hall | Garrett Wilson | Michael Pittman Jr. | Tre' Harris | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">C.J. Stroud | Kenneth Walker III | Breece Hall | Garrett Wilson | Parker Washington | Ladd McConkey | Travis Kelce | Dalton Schultz | Seahawks</t>
         </is>
       </c>
     </row>
@@ -1142,13 +1142,13 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>49600</v>
+        <v>49900</v>
       </c>
       <c r="C35">
-        <v>162.798</v>
+        <v>160.5396</v>
       </c>
       <c r="D35">
-        <v>156.5606</v>
+        <v>150.9224</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Garrett Wilson | Parker Washington | Tre' Harris | Travis Kelce | Dalton Schultz | Bengals</t>
+          <t xml:space="preserve">Deshaun Watson | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Michael Pittman Jr. | Travis Kelce | Dalton Schultz | Seahawks</t>
         </is>
       </c>
     </row>
@@ -1166,22 +1166,22 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>49500</v>
+        <v>50000</v>
       </c>
       <c r="C36">
-        <v>162.586</v>
+        <v>158.4838</v>
       </c>
       <c r="D36">
-        <v>150.0189</v>
+        <v>143.9699</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALUE_FRONTIER</t>
+          <t xml:space="preserve">BEST_WITH_RB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Jaylin Noel | Travis Kelce | Dalton Schultz | Panthers</t>
+          <t xml:space="preserve">Patrick Mahomes | Jonathan Taylor | Kenneth Walker III | Amon-Ra St. Brown | Ladd McConkey | Jaylin Noel | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -1190,22 +1190,22 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>50000</v>
+        <v>49700</v>
       </c>
       <c r="C37">
-        <v>162.3068</v>
+        <v>159.1044</v>
       </c>
       <c r="D37">
-        <v>151.4813</v>
+        <v>152.6632</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALUE_FRONTIER</t>
+          <t xml:space="preserve">BEST_WITH_WR</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Rashee Rice | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Bengals</t>
+          <t xml:space="preserve">Patrick Mahomes | Jahmyr Gibbs | Kenneth Walker III | Garrett Wilson | Josh Downs | Tre' Harris | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -1214,22 +1214,22 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>49500</v>
+        <v>49900</v>
       </c>
       <c r="C38">
-        <v>162.2817</v>
+        <v>159.4396</v>
       </c>
       <c r="D38">
-        <v>152.7547</v>
+        <v>153.8758</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALUE_FRONTIER</t>
+          <t xml:space="preserve">BEST_WITH_DST</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Patriots</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Dolphins</t>
         </is>
       </c>
     </row>
@@ -1238,13 +1238,13 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>49900</v>
+        <v>49600</v>
       </c>
       <c r="C39">
-        <v>162.0233</v>
+        <v>162.798</v>
       </c>
       <c r="D39">
-        <v>153.9821</v>
+        <v>157.4556</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Seahawks</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Garrett Wilson | Parker Washington | Tre' Harris | Travis Kelce | Dalton Schultz | Bengals</t>
         </is>
       </c>
     </row>
@@ -1262,13 +1262,13 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>49700</v>
+        <v>49800</v>
       </c>
       <c r="C40">
-        <v>161.9668</v>
+        <v>161.9198</v>
       </c>
       <c r="D40">
-        <v>151.3119</v>
+        <v>155.1781</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Jahmyr Gibbs | Kenneth Walker III | Garrett Wilson | Tre' Harris | Jaylin Noel | Travis Kelce | Dalton Schultz | Panthers</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Garrett Wilson | Ladd McConkey | Tre' Harris | Travis Kelce | Dalton Schultz | Texans</t>
         </is>
       </c>
     </row>
@@ -1286,13 +1286,13 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>49900</v>
+        <v>50000</v>
       </c>
       <c r="C41">
-        <v>161.7661</v>
+        <v>161.5618</v>
       </c>
       <c r="D41">
-        <v>153.1259</v>
+        <v>148.674</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Jahmyr Gibbs | Kenneth Walker III | Garrett Wilson | Ladd McConkey | Tre' Harris | Travis Kelce | Dalton Schultz | Patriots</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Jaylen Warren | Amon-Ra St. Brown | Parker Washington | Jaylin Noel | Travis Kelce | Dalton Schultz | Steelers</t>
         </is>
       </c>
     </row>
@@ -1313,10 +1313,10 @@
         <v>49900</v>
       </c>
       <c r="C42">
-        <v>161.7567</v>
+        <v>161.2901</v>
       </c>
       <c r="D42">
-        <v>153.9868</v>
+        <v>153.3625</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marcus Mariota | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Garrett Wilson | Parker Washington | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Patrick Mahomes | Jahmyr Gibbs | Kenneth Walker III | Parker Washington | Ladd McConkey | Tre' Harris | Travis Kelce | Dalton Schultz | Panthers</t>
         </is>
       </c>
     </row>
@@ -1334,13 +1334,13 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>49900</v>
+        <v>50000</v>
       </c>
       <c r="C43">
-        <v>161.6981</v>
+        <v>161.1401</v>
       </c>
       <c r="D43">
-        <v>148.384</v>
+        <v>151.8785</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Michael Pittman Jr. | Tre' Harris | Travis Kelce | Dalton Schultz | Bengals</t>
+          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Jaxon Smith-Njigba | Ladd McConkey | Tre' Harris | Travis Kelce | Dalton Schultz | Bengals</t>
         </is>
       </c>
     </row>
@@ -1358,13 +1358,13 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>49800</v>
+        <v>50000</v>
       </c>
       <c r="C44">
-        <v>161.5427</v>
+        <v>160.9691</v>
       </c>
       <c r="D44">
-        <v>149.8101</v>
+        <v>152.3545</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Breece Hall | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Ladd McConkey | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Patrick Mahomes | Jahmyr Gibbs | Breece Hall | Garrett Wilson | Ladd McConkey | Tre' Harris | Travis Kelce | Dalton Schultz | Seahawks</t>
         </is>
       </c>
     </row>
@@ -1382,13 +1382,13 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>49900</v>
+        <v>50000</v>
       </c>
       <c r="C45">
-        <v>161.5365</v>
+        <v>160.8618</v>
       </c>
       <c r="D45">
-        <v>151.0826</v>
+        <v>150.3282</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Breece Hall | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Parker Washington | Travis Kelce | Dalton Schultz | Steelers</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Parker Washington | Ladd McConkey | Michael Pittman Jr. | Travis Kelce | Dalton Schultz | Bengals</t>
         </is>
       </c>
     </row>
@@ -1406,13 +1406,13 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>49200</v>
+        <v>49800</v>
       </c>
       <c r="C46">
-        <v>161.4464</v>
+        <v>160.8536</v>
       </c>
       <c r="D46">
-        <v>150.6548</v>
+        <v>150.5031</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Garrett Wilson | Ladd McConkey | Jaylin Noel | Travis Kelce | Dalton Schultz | Bengals</t>
+          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Jaylen Warren | Amon-Ra St. Brown | Garrett Wilson | Michael Pittman Jr. | Travis Kelce | Dalton Schultz | Bengals</t>
         </is>
       </c>
     </row>
@@ -1433,10 +1433,10 @@
         <v>49900</v>
       </c>
       <c r="C47">
-        <v>161.2901</v>
+        <v>160.8466</v>
       </c>
       <c r="D47">
-        <v>152.6175</v>
+        <v>153.3092</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Jahmyr Gibbs | Kenneth Walker III | Parker Washington | Ladd McConkey | Tre' Harris | Travis Kelce | Dalton Schultz | Panthers</t>
+          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Breece Hall | Garrett Wilson | Parker Washington | Michael Pittman Jr. | Travis Kelce | Dalton Schultz | Titans</t>
         </is>
       </c>
     </row>
@@ -1454,13 +1454,13 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>49900</v>
+        <v>49700</v>
       </c>
       <c r="C48">
-        <v>161.1249</v>
+        <v>160.7154</v>
       </c>
       <c r="D48">
-        <v>154.0495</v>
+        <v>152.0738</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Jaxon Smith-Njigba | Garrett Wilson | Tre' Harris | Travis Kelce | Dalton Schultz | Titans</t>
+          <t xml:space="preserve">Patrick Mahomes | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Parker Washington | Tre' Harris | Travis Kelce | Dalton Schultz | Texans</t>
         </is>
       </c>
     </row>
@@ -1478,13 +1478,13 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>49800</v>
+        <v>50000</v>
       </c>
       <c r="C49">
-        <v>161.0834</v>
+        <v>160.6925</v>
       </c>
       <c r="D49">
-        <v>155.953</v>
+        <v>153.7199</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Josh Allen | Kenneth Walker III | Jaylen Warren | Garrett Wilson | Parker Washington | Tre' Harris | Travis Kelce | Dalton Schultz | Seahawks</t>
+          <t xml:space="preserve">Deshaun Watson | Kenneth Walker III | Breece Hall | Amon-Ra St. Brown | Parker Washington | Ladd McConkey | Travis Kelce | Dalton Schultz | Panthers</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.5</v>
+        <v>0.5125</v>
       </c>
       <c r="C2">
         <v>162.7486</v>
@@ -1574,13 +1574,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.77</v>
+        <v>0.775</v>
       </c>
       <c r="C3">
-        <v>161.0701</v>
+        <v>160.9078</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E3">
         <v>1.0</v>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.8875</v>
+        <v>0.89</v>
       </c>
       <c r="C6">
-        <v>0.7225</v>
+        <v>0.73</v>
       </c>
       <c r="D6">
-        <v>0.4792</v>
+        <v>0.3333</v>
       </c>
       <c r="E6"/>
     </row>
@@ -1623,13 +1623,13 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.7025</v>
+        <v>0.7225</v>
       </c>
       <c r="C7">
-        <v>0.3625</v>
+        <v>0.3825</v>
       </c>
       <c r="D7">
-        <v>0.5</v>
+        <v>0.4583</v>
       </c>
       <c r="E7"/>
     </row>
@@ -1640,13 +1640,13 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.8775</v>
+        <v>0.875</v>
       </c>
       <c r="C8">
-        <v>0.635</v>
+        <v>0.6425</v>
       </c>
       <c r="D8">
-        <v>0.5833</v>
+        <v>0.5</v>
       </c>
       <c r="E8"/>
     </row>
@@ -1657,13 +1657,13 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="C9">
-        <v>0.4975</v>
+        <v>0.5075</v>
       </c>
       <c r="D9">
-        <v>0.5625</v>
+        <v>0.5417</v>
       </c>
       <c r="E9"/>
     </row>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>12.67</v>
+        <v>17.58</v>
       </c>
       <c r="E2">
         <v>336</v>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>12.55</v>
+        <v>17.46</v>
       </c>
       <c r="E3">
         <v>336</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>12.53</v>
+        <v>17.44</v>
       </c>
       <c r="E4">
         <v>336</v>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>12.49</v>
+        <v>17.4</v>
       </c>
       <c r="E5">
         <v>720</v>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>10.74</v>
+        <v>15.65</v>
       </c>
       <c r="E6">
         <v>336</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>10.93</v>
+        <v>15.84</v>
       </c>
       <c r="E7">
         <v>336</v>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>10.71</v>
+        <v>15.62</v>
       </c>
       <c r="E8">
         <v>336</v>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>10.61</v>
+        <v>0.11</v>
       </c>
       <c r="E9">
         <v>336</v>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>10.98</v>
+        <v>15.89</v>
       </c>
       <c r="E10">
         <v>720</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.49</v>
+        <v>1.03</v>
       </c>
       <c r="E11">
         <v>168</v>
@@ -1989,12 +1989,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">SLATE</t>
+          <t xml:space="preserve">MODEL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">slate.projection</t>
+          <t xml:space="preserve">derived.role_state</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.15</v>
+        <v>0.98</v>
       </c>
       <c r="E12">
         <v>36</v>
@@ -2022,19 +2022,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">slate.post_inactives</t>
+          <t xml:space="preserve">slate.projection</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">STALE</t>
+          <t xml:space="preserve">FRESH_BUT_BEHIND_ITS_INPUTS</t>
         </is>
       </c>
       <c r="D13">
-        <v>21.61</v>
+        <v>5.06</v>
       </c>
       <c r="E13">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2050,19 +2050,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">field.model</t>
+          <t xml:space="preserve">slate.post_inactives</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRESH</t>
+          <t xml:space="preserve">STALE</t>
         </is>
       </c>
       <c r="D14">
-        <v>0.04</v>
+        <v>26.52</v>
       </c>
       <c r="E14">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2073,63 +2073,91 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t xml:space="preserve">SLATE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">field.model</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRESH</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>4.95</v>
+      </c>
+      <c r="E15">
+        <v>36</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FILE_MTIME_FALLBACK_ARTIFACT_STATES_NO_CUTOFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t xml:space="preserve">DECISION</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t xml:space="preserve">portfolio.contest</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">FRESH</t>
         </is>
       </c>
-      <c r="D15">
+      <c r="D16">
         <v>0.01</v>
       </c>
-      <c r="E15">
+      <c r="E16">
         <v>24</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t xml:space="preserve">FILE_MTIME_FALLBACK_ARTIFACT_STATES_NO_CUTOFF</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRODUCT MODE</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PARTIAL</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">BECAUSE</t>
+          <t xml:space="preserve">PRODUCT MODE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">the model layer is intact but slate-level artifacts are not fresh: ['slate.post_inactives']</t>
+          <t xml:space="preserve">PARTIAL</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t xml:space="preserve">BECAUSE</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the model layer is intact but slate-level artifacts are not fresh: ['slate.projection', 'slate.post_inactives']</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t xml:space="preserve">SATURDAY RULE</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t xml:space="preserve">PASS SATURDAY_RULE_MET</t>
         </is>
@@ -2209,7 +2237,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>1790604240</v>
+        <v>1790621916</v>
       </c>
     </row>
     <row r="7">
@@ -2239,12 +2267,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">dst_scores_are_floors</t>
+          <t xml:space="preserve">dst_scoring_tail</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">defensive and return touchdowns are excluded; see OUT-041</t>
+          <t xml:space="preserve">defensive and return touchdowns and safeties are MEASURED from play-by-play, not excluded; OUT-041 closed 2026-09-28</t>
         </is>
       </c>
     </row>

--- a/nfl/dfs/salaries/DK_WEEK3_DELIVERABLE_SUPPLEMENT.xlsx
+++ b/nfl/dfs/salaries/DK_WEEK3_DELIVERABLE_SUPPLEMENT.xlsx
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>17.58</v>
+        <v>18.75</v>
       </c>
       <c r="E2">
         <v>336</v>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>17.46</v>
+        <v>18.63</v>
       </c>
       <c r="E3">
         <v>336</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>17.44</v>
+        <v>18.61</v>
       </c>
       <c r="E4">
         <v>336</v>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>17.4</v>
+        <v>18.56</v>
       </c>
       <c r="E5">
         <v>720</v>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>15.65</v>
+        <v>16.82</v>
       </c>
       <c r="E6">
         <v>336</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>15.84</v>
+        <v>17.0</v>
       </c>
       <c r="E7">
         <v>336</v>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>15.62</v>
+        <v>16.79</v>
       </c>
       <c r="E8">
         <v>336</v>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.11</v>
+        <v>1.28</v>
       </c>
       <c r="E9">
         <v>336</v>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>15.89</v>
+        <v>17.06</v>
       </c>
       <c r="E10">
         <v>720</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>1.03</v>
+        <v>2.19</v>
       </c>
       <c r="E11">
         <v>168</v>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.98</v>
+        <v>2.15</v>
       </c>
       <c r="E12">
         <v>36</v>
@@ -2027,11 +2027,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRESH_BUT_BEHIND_ITS_INPUTS</t>
+          <t xml:space="preserve">FRESH</t>
         </is>
       </c>
       <c r="D13">
-        <v>5.06</v>
+        <v>0.78</v>
       </c>
       <c r="E13">
         <v>36</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="D14">
-        <v>26.52</v>
+        <v>27.69</v>
       </c>
       <c r="E14">
         <v>6</v>
@@ -2083,11 +2083,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRESH</t>
+          <t xml:space="preserve">FRESH_BUT_BEHIND_ITS_INPUTS</t>
         </is>
       </c>
       <c r="D15">
-        <v>4.95</v>
+        <v>6.12</v>
       </c>
       <c r="E15">
         <v>36</v>
@@ -2111,11 +2111,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRESH</t>
+          <t xml:space="preserve">FRESH_BUT_BEHIND_ITS_INPUTS</t>
         </is>
       </c>
       <c r="D16">
-        <v>0.01</v>
+        <v>1.18</v>
       </c>
       <c r="E16">
         <v>24</v>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">the model layer is intact but slate-level artifacts are not fresh: ['slate.projection', 'slate.post_inactives']</t>
+          <t xml:space="preserve">the model layer is intact but slate-level artifacts are not fresh: ['slate.post_inactives', 'field.model', 'portfolio.contest']</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>1790621916</v>
+        <v>1790626119</v>
       </c>
     </row>
     <row r="7">

--- a/nfl/dfs/salaries/DK_WEEK3_DELIVERABLE_SUPPLEMENT.xlsx
+++ b/nfl/dfs/salaries/DK_WEEK3_DELIVERABLE_SUPPLEMENT.xlsx
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>18.75</v>
+        <v>22.18</v>
       </c>
       <c r="E2">
         <v>336</v>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>18.63</v>
+        <v>22.06</v>
       </c>
       <c r="E3">
         <v>336</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>18.61</v>
+        <v>22.04</v>
       </c>
       <c r="E4">
         <v>336</v>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>18.56</v>
+        <v>21.99</v>
       </c>
       <c r="E5">
         <v>720</v>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>16.82</v>
+        <v>20.25</v>
       </c>
       <c r="E6">
         <v>336</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>17.0</v>
+        <v>20.43</v>
       </c>
       <c r="E7">
         <v>336</v>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>16.79</v>
+        <v>20.21</v>
       </c>
       <c r="E8">
         <v>336</v>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>1.28</v>
+        <v>4.71</v>
       </c>
       <c r="E9">
         <v>336</v>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>17.06</v>
+        <v>20.49</v>
       </c>
       <c r="E10">
         <v>720</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>2.19</v>
+        <v>5.62</v>
       </c>
       <c r="E11">
         <v>168</v>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="D12">
-        <v>2.15</v>
+        <v>5.58</v>
       </c>
       <c r="E12">
         <v>36</v>
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.78</v>
+        <v>4.21</v>
       </c>
       <c r="E13">
         <v>36</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="D14">
-        <v>27.69</v>
+        <v>31.12</v>
       </c>
       <c r="E14">
         <v>6</v>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>6.12</v>
+        <v>9.55</v>
       </c>
       <c r="E15">
         <v>36</v>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="D16">
-        <v>1.18</v>
+        <v>4.61</v>
       </c>
       <c r="E16">
         <v>24</v>
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>1790626119</v>
+        <v>1790638463</v>
       </c>
     </row>
     <row r="7">

--- a/nfl/dfs/salaries/DK_WEEK3_DELIVERABLE_SUPPLEMENT.xlsx
+++ b/nfl/dfs/salaries/DK_WEEK3_DELIVERABLE_SUPPLEMENT.xlsx
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>22.18</v>
+        <v>22.39</v>
       </c>
       <c r="E2">
         <v>336</v>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>22.06</v>
+        <v>22.27</v>
       </c>
       <c r="E3">
         <v>336</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>22.04</v>
+        <v>22.25</v>
       </c>
       <c r="E4">
         <v>336</v>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>21.99</v>
+        <v>22.2</v>
       </c>
       <c r="E5">
         <v>720</v>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>20.25</v>
+        <v>20.46</v>
       </c>
       <c r="E6">
         <v>336</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>20.43</v>
+        <v>20.64</v>
       </c>
       <c r="E7">
         <v>336</v>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>20.21</v>
+        <v>20.42</v>
       </c>
       <c r="E8">
         <v>336</v>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>4.71</v>
+        <v>4.92</v>
       </c>
       <c r="E9">
         <v>336</v>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>20.49</v>
+        <v>20.7</v>
       </c>
       <c r="E10">
         <v>720</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>5.62</v>
+        <v>5.83</v>
       </c>
       <c r="E11">
         <v>168</v>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="D12">
-        <v>5.58</v>
+        <v>5.79</v>
       </c>
       <c r="E12">
         <v>36</v>
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="D13">
-        <v>4.21</v>
+        <v>4.42</v>
       </c>
       <c r="E13">
         <v>36</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="D14">
-        <v>31.12</v>
+        <v>31.33</v>
       </c>
       <c r="E14">
         <v>6</v>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>9.55</v>
+        <v>9.76</v>
       </c>
       <c r="E15">
         <v>36</v>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="D16">
-        <v>4.61</v>
+        <v>4.82</v>
       </c>
       <c r="E16">
         <v>24</v>
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>1790638463</v>
+        <v>1790639218</v>
       </c>
     </row>
     <row r="7">

--- a/nfl/dfs/salaries/DK_WEEK3_DELIVERABLE_SUPPLEMENT.xlsx
+++ b/nfl/dfs/salaries/DK_WEEK3_DELIVERABLE_SUPPLEMENT.xlsx
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>22.39</v>
+        <v>23.58</v>
       </c>
       <c r="E2">
         <v>336</v>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>22.27</v>
+        <v>23.46</v>
       </c>
       <c r="E3">
         <v>336</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>22.25</v>
+        <v>23.44</v>
       </c>
       <c r="E4">
         <v>336</v>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>22.2</v>
+        <v>23.4</v>
       </c>
       <c r="E5">
         <v>720</v>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>20.46</v>
+        <v>21.65</v>
       </c>
       <c r="E6">
         <v>336</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>20.64</v>
+        <v>21.84</v>
       </c>
       <c r="E7">
         <v>336</v>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>20.42</v>
+        <v>21.62</v>
       </c>
       <c r="E8">
         <v>336</v>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>4.92</v>
+        <v>6.11</v>
       </c>
       <c r="E9">
         <v>336</v>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>20.7</v>
+        <v>21.89</v>
       </c>
       <c r="E10">
         <v>720</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>5.83</v>
+        <v>7.03</v>
       </c>
       <c r="E11">
         <v>168</v>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="D12">
-        <v>5.79</v>
+        <v>6.98</v>
       </c>
       <c r="E12">
         <v>36</v>
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="D13">
-        <v>4.42</v>
+        <v>5.61</v>
       </c>
       <c r="E13">
         <v>36</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="D14">
-        <v>31.33</v>
+        <v>32.52</v>
       </c>
       <c r="E14">
         <v>6</v>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>9.76</v>
+        <v>10.95</v>
       </c>
       <c r="E15">
         <v>36</v>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="D16">
-        <v>4.82</v>
+        <v>6.01</v>
       </c>
       <c r="E16">
         <v>24</v>
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>1790639218</v>
+        <v>1790643515</v>
       </c>
     </row>
     <row r="7">

--- a/nfl/dfs/salaries/DK_WEEK3_DELIVERABLE_SUPPLEMENT.xlsx
+++ b/nfl/dfs/salaries/DK_WEEK3_DELIVERABLE_SUPPLEMENT.xlsx
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>23.58</v>
+        <v>91.5</v>
       </c>
       <c r="E2">
         <v>336</v>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>23.46</v>
+        <v>91.39</v>
       </c>
       <c r="E3">
         <v>336</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>23.44</v>
+        <v>91.37</v>
       </c>
       <c r="E4">
         <v>336</v>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>23.4</v>
+        <v>91.32</v>
       </c>
       <c r="E5">
         <v>720</v>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>21.65</v>
+        <v>89.57</v>
       </c>
       <c r="E6">
         <v>336</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>21.84</v>
+        <v>89.76</v>
       </c>
       <c r="E7">
         <v>336</v>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>21.62</v>
+        <v>89.54</v>
       </c>
       <c r="E8">
         <v>336</v>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>6.11</v>
+        <v>74.04</v>
       </c>
       <c r="E9">
         <v>336</v>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>21.89</v>
+        <v>89.81</v>
       </c>
       <c r="E10">
         <v>720</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>7.03</v>
+        <v>74.95</v>
       </c>
       <c r="E11">
         <v>168</v>
@@ -1999,11 +1999,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRESH</t>
+          <t xml:space="preserve">STALE</t>
         </is>
       </c>
       <c r="D12">
-        <v>6.98</v>
+        <v>74.91</v>
       </c>
       <c r="E12">
         <v>36</v>
@@ -2027,11 +2027,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRESH</t>
+          <t xml:space="preserve">STALE</t>
         </is>
       </c>
       <c r="D13">
-        <v>5.61</v>
+        <v>73.54</v>
       </c>
       <c r="E13">
         <v>36</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="D14">
-        <v>32.52</v>
+        <v>100.45</v>
       </c>
       <c r="E14">
         <v>6</v>
@@ -2083,11 +2083,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRESH_BUT_BEHIND_ITS_INPUTS</t>
+          <t xml:space="preserve">STALE</t>
         </is>
       </c>
       <c r="D15">
-        <v>10.95</v>
+        <v>78.87</v>
       </c>
       <c r="E15">
         <v>36</v>
@@ -2111,11 +2111,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRESH_BUT_BEHIND_ITS_INPUTS</t>
+          <t xml:space="preserve">STALE</t>
         </is>
       </c>
       <c r="D16">
-        <v>6.01</v>
+        <v>73.94</v>
       </c>
       <c r="E16">
         <v>24</v>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">the model layer is intact but slate-level artifacts are not fresh: ['slate.post_inactives', 'field.model', 'portfolio.contest']</t>
+          <t xml:space="preserve">the model layer is intact but slate-level artifacts are not fresh: ['slate.projection', 'slate.post_inactives', 'field.model', 'portfolio.contest']</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>1790643515</v>
+        <v>1790888040</v>
       </c>
     </row>
     <row r="7">

--- a/nfl/dfs/salaries/DK_WEEK3_DELIVERABLE_SUPPLEMENT.xlsx
+++ b/nfl/dfs/salaries/DK_WEEK3_DELIVERABLE_SUPPLEMENT.xlsx
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>91.5</v>
+        <v>33.95</v>
       </c>
       <c r="E2">
         <v>336</v>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>91.39</v>
+        <v>33.84</v>
       </c>
       <c r="E3">
         <v>336</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>91.37</v>
+        <v>33.84</v>
       </c>
       <c r="E4">
         <v>336</v>
@@ -1803,11 +1803,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRESH</t>
+          <t xml:space="preserve">FRESH_BUT_BEHIND_ITS_INPUTS</t>
         </is>
       </c>
       <c r="D5">
-        <v>91.32</v>
+        <v>125.82</v>
       </c>
       <c r="E5">
         <v>720</v>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>89.57</v>
+        <v>33.8</v>
       </c>
       <c r="E6">
         <v>336</v>
@@ -1859,11 +1859,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRESH</t>
+          <t xml:space="preserve">FRESH_BUT_BEHIND_ITS_INPUTS</t>
         </is>
       </c>
       <c r="D7">
-        <v>89.76</v>
+        <v>124.26</v>
       </c>
       <c r="E7">
         <v>336</v>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>89.54</v>
+        <v>33.8</v>
       </c>
       <c r="E8">
         <v>336</v>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>74.04</v>
+        <v>33.8</v>
       </c>
       <c r="E9">
         <v>336</v>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>89.81</v>
+        <v>33.8</v>
       </c>
       <c r="E10">
         <v>720</v>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRESH</t>
+          <t xml:space="preserve">FRESH_BUT_BEHIND_ITS_INPUTS</t>
         </is>
       </c>
       <c r="D11">
-        <v>74.95</v>
+        <v>109.45</v>
       </c>
       <c r="E11">
         <v>168</v>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="D12">
-        <v>74.91</v>
+        <v>109.41</v>
       </c>
       <c r="E12">
         <v>36</v>
@@ -2027,11 +2027,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">STALE</t>
+          <t xml:space="preserve">FRESH</t>
         </is>
       </c>
       <c r="D13">
-        <v>73.54</v>
+        <v>25.96</v>
       </c>
       <c r="E13">
         <v>36</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="D14">
-        <v>100.45</v>
+        <v>134.95</v>
       </c>
       <c r="E14">
         <v>6</v>
@@ -2087,7 +2087,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>78.87</v>
+        <v>113.38</v>
       </c>
       <c r="E15">
         <v>36</v>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="D16">
-        <v>73.94</v>
+        <v>108.44</v>
       </c>
       <c r="E16">
         <v>24</v>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">the model layer is intact but slate-level artifacts are not fresh: ['slate.projection', 'slate.post_inactives', 'field.model', 'portfolio.contest']</t>
+          <t xml:space="preserve">the model layer is intact but slate-level artifacts are not fresh: ['slate.post_inactives', 'field.model', 'portfolio.contest']</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>1790888040</v>
+        <v>1791012243</v>
       </c>
     </row>
     <row r="7">
